--- a/employment_forms/044_work_release_form--employment_forms.xlsx
+++ b/employment_forms/044_work_release_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>employerdate</t>
+          <t>employerdate_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>employeename</t>
+          <t>employeename_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Employee name</t>
+          <t>Employeename 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>employername</t>
+          <t>employername_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Employer name</t>
+          <t>Employername 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Employee name</t>
+          <t>Employeename3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>employeename2</t>
+          <t>employeename2_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Employee name</t>
+          <t>Employeename2 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>employeename</t>
+          <t>employeename_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>employername2</t>
+          <t>employername2_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>employername</t>
+          <t>employername_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Employer</t>
+          <t>Employername 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'reason_for_leave':_'family_obligation'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'Reason for Leave': 'Family Obligation'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'reason_for_leave':_'jury_duty'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'Reason for Leave': 'Jury Duty'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'reason_for_leave':_'medical'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'Reason for Leave': 'Medical'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'reason_for_leave':_'military_leave'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'Reason for Leave': 'Military Leave'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'reason_for_leave':_'other'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'Reason for Leave': 'Other'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'reason_for_leave':_'family_obligation'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'Reason for Leave': 'Family Obligation'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'reason_for_leave':_'jury_duty'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'Reason for Leave': 'Jury Duty'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'reason_for_leave':_'medical'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'Reason for Leave': 'Medical'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'reason_for_leave':_'military_leave'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'Reason for Leave': 'Military Leave'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'reason_for_leave':_'other'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'Reason for Leave': 'Other'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
